--- a/resources/templates/heyman/deregistration_application.xlsx
+++ b/resources/templates/heyman/deregistration_application.xlsx
@@ -146,7 +146,40 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">[v]수출 예정 [ ]도난</t>
+      <rPr>
+        <rFont val="돋움"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">[v]</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="돋움"/>
+        <b val="true"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">수출 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="돋움"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve"> [ ]도난</t>
     </r>
   </si>
   <si>
@@ -2318,7 +2351,40 @@
       <c r="B14" s="19" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">[v]수출 예정 [ ]도난</t>
+            <rPr>
+              <rFont val="돋움"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="11"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">[v]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="돋움"/>
+              <b val="true"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="11"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">수출 예정</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="돋움"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="11"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve"> [ ]도난</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/deregistration_application.xlsx
+++ b/resources/templates/heyman/deregistration_application.xlsx
@@ -299,7 +299,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">경기도 시흥시 산기대학로 163, 328호(정왕동)</t>
+      <t xml:space="preserve">서울특별시 마포구 매봉산로 31, 에스플랙스센터 시너지움 7층 1인 미디어파트너스 (상암동)</t>
     </r>
   </si>
   <si>
@@ -317,7 +317,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">662-81-00898</t>
+      <t xml:space="preserve">535-87-01734</t>
     </r>
   </si>
   <si>
@@ -2798,7 +2798,7 @@
       <c r="C34" s="29" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">경기도 시흥시 산기대학로 163, 328호(정왕동)</t>
+            <t xml:space="preserve">서울특별시 마포구 매봉산로 31, 에스플랙스센터 시너지움 7층 1인 미디어파트너스 (상암동)</t>
           </r>
         </is>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="C36" s="110" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">662-81-00898</t>
+            <t xml:space="preserve">535-87-01734</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/deregistration_application.xlsx
+++ b/resources/templates/heyman/deregistration_application.xlsx
@@ -2780,7 +2780,7 @@
       <c r="L33" s="103"/>
       <c r="M33" s="104"/>
     </row>
-    <row r="34" spans="1:17" customHeight="1" ht="27" s="32" customFormat="1">
+    <row r="34" spans="1:17" customHeight="1" ht="39" s="32" customFormat="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
           <r>

--- a/resources/templates/heyman/deregistration_application.xlsx
+++ b/resources/templates/heyman/deregistration_application.xlsx
@@ -299,7 +299,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">서울특별시 마포구 매봉산로 31, 에스플랙스센터 시너지움 7층 1인 미디어파트너스 (상암동)</t>
+      <t xml:space="preserve">서울특별시 영등포구 선유동1로 50, 513호(당산동3가, THE PARK 365)</t>
     </r>
   </si>
   <si>
@@ -2798,7 +2798,7 @@
       <c r="C34" s="29" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">서울특별시 마포구 매봉산로 31, 에스플랙스센터 시너지움 7층 1인 미디어파트너스 (상암동)</t>
+            <t xml:space="preserve">서울특별시 영등포구 선유동1로 50, 513호(당산동3가, THE PARK 365)</t>
           </r>
         </is>
       </c>
